--- a/scripts/memes.xlsx
+++ b/scripts/memes.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="55">
   <si>
     <t>group_keyword</t>
   </si>
@@ -67,13 +67,133 @@
   <si>
     <t>點,車,car</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴斯光年</t>
+  </si>
+  <si>
+    <t>ㄅㄚㄙㄍㄨㄤㄋ一ㄢˊ</t>
+  </si>
+  <si>
+    <t>動漫</t>
+  </si>
+  <si>
+    <t>綜合</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/2rydFHVENSy8OU4pmWUhSq.png</t>
+  </si>
+  <si>
+    <t>玩具總動員</t>
+  </si>
+  <si>
+    <t>剩下光年</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/5CTUgRhSFRRmzNYt1VAhOG.png</t>
+  </si>
+  <si>
+    <t>盛夏光年,夏天</t>
+  </si>
+  <si>
+    <t>賽巴斯欽</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/4VvMWlVNiwU00qkPyGqnaB.png</t>
+  </si>
+  <si>
+    <t>執事</t>
+  </si>
+  <si>
+    <t>巴斯嗑乳酪蛋糕</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/7xVNtnbchsUtfvW0RTBuCH.png</t>
+  </si>
+  <si>
+    <t>甜點</t>
+  </si>
+  <si>
+    <t>殺龍巴斯</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/4uKGMpJtuDNFLr9WzUuTQ4.png</t>
+  </si>
+  <si>
+    <t>戰士</t>
+  </si>
+  <si>
+    <t>水餃</t>
+  </si>
+  <si>
+    <t>ㄕㄨㄟˇㄐㄧㄠˇ</t>
+  </si>
+  <si>
+    <t>食物</t>
+  </si>
+  <si>
+    <t>邊邊餃餃</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/4Bhev8McQRHYGUQMTmAA6Q.jpg</t>
+  </si>
+  <si>
+    <t>邊邊角角</t>
+  </si>
+  <si>
+    <t>面容餃好</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/77P35TiQUxJhuTp0m7xEHq.jpg</t>
+  </si>
+  <si>
+    <t>皮被擀</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/2ifgDDqav6ggceoZGFRxne.jpg</t>
+  </si>
+  <si>
+    <t>疲憊感,社畜</t>
+  </si>
+  <si>
+    <t>蒸煎炸</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/7kIBxewysK84Mo4hBPFu1r.png</t>
+  </si>
+  <si>
+    <t>社畜</t>
+  </si>
+  <si>
+    <t>餃網過正</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3rmnzfNiQGeoYRgVWutTMl.png</t>
+  </si>
+  <si>
+    <t>本日的主餃</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1dOeKp6PBwyvOzFdj1sXn2.png</t>
+  </si>
+  <si>
+    <t>本日的主角,生日</t>
+  </si>
+  <si>
+    <t>餃安</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/Uw0yDWoKQBL5mTu8F2EPP.png</t>
+  </si>
+  <si>
+    <t>早安,歐嗨喲,禮貌</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -101,6 +221,14 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="3">
@@ -141,12 +269,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -156,9 +288,20 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -450,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
@@ -463,7 +606,7 @@
     <col min="8" max="8" width="22.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="39" thickBot="1">
+    <row r="1" spans="1:26" ht="17.25" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +650,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:26" ht="17.25" thickBot="1">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -533,10 +676,352 @@
         <v>14</v>
       </c>
     </row>
+    <row r="3" spans="1:26" ht="33.75" thickBot="1">
+      <c r="A3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="33.75" thickBot="1">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="33.75" thickBot="1">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="33.75" thickBot="1">
+      <c r="A6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="33.75" thickBot="1">
+      <c r="A7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="33.75" thickBot="1">
+      <c r="A8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="17.25" thickBot="1">
+      <c r="A9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:26" ht="33.75" thickBot="1">
+      <c r="A10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="33.75" thickBot="1">
+      <c r="A11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="17.25" thickBot="1">
+      <c r="A12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:26" ht="33.75" thickBot="1">
+      <c r="A13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="33.75" thickBot="1">
+      <c r="A14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="17.25" thickBot="1">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:26" ht="17.25" thickBot="1">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G3" r:id="rId1"/>
+    <hyperlink ref="G4" r:id="rId2"/>
+    <hyperlink ref="G5" r:id="rId3"/>
+    <hyperlink ref="G6" r:id="rId4"/>
+    <hyperlink ref="G7" r:id="rId5"/>
+    <hyperlink ref="G8" r:id="rId6"/>
+    <hyperlink ref="G9" r:id="rId7"/>
+    <hyperlink ref="G10" r:id="rId8"/>
+    <hyperlink ref="G11" r:id="rId9"/>
+    <hyperlink ref="G12" r:id="rId10"/>
+    <hyperlink ref="G13" r:id="rId11"/>
+    <hyperlink ref="G14" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>
 

--- a/scripts/memes.xlsx
+++ b/scripts/memes.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="183">
   <si>
     <t>group_keyword</t>
   </si>
@@ -153,9 +153,6 @@
     <t>https://images.plurk.com/2ifgDDqav6ggceoZGFRxne.jpg</t>
   </si>
   <si>
-    <t>疲憊感,社畜</t>
-  </si>
-  <si>
     <t>蒸煎炸</t>
   </si>
   <si>
@@ -187,13 +184,620 @@
   </si>
   <si>
     <t>早安,歐嗨喲,禮貌</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/2gnd2P6kqYUIP6YJuPBpDJ.jpg</t>
+  </si>
+  <si>
+    <t>笑鼠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1WiMO8GIViPuSvJomkjVDH.jpg</t>
+  </si>
+  <si>
+    <t>氣鼠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/6DCdDGpyMr8frBL9Nc0hVz.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>家鼠答禮</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>禮貌,家屬答禮</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/5CT6odV9237lc5rgrI0SUc.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>哈根大鼠</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/cKjBsoFSAaTjavclYiYFt.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>YBSG,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>辣妹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,Y2K</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>やば鼠ぎ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/5qaiXPrnt0C6PVNxHvbg1i.gif</t>
+  </si>
+  <si>
+    <t>摳鼠洞</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>COLDSTONE,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>冰淇淋</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>動物</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>哈根達斯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>冰淇淋</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>勞贖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹹食</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>笑鼠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄠˋㄕㄨˇ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐鼠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄋㄞˋㄕㄨˇ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/25MfDyxEofAdzcYH7ZBUc1.jpg</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3dX1MtxhovBKZ3rGthsl5m.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>累鼠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>疲勞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>社畜</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/rnAA2npWWg7hO9PJnyZQC.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>普立鼠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/7DZbXquRZm5W3OmXDfBXod.jpg</t>
+  </si>
+  <si>
+    <t>灑幣鼠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1OKltdvOCGqk8amLhodrTf.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>重金鼠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/6rBotfUQpJSEN2Vp0Lm4nn.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>蝦米EAT鼠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>樂團</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SERVICE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>什麼意思</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>疲勞</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>拜託,禮貌,社畜</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>社畜</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1FK4sibXzkUCReqaU9BEDa.png</t>
+  </si>
+  <si>
+    <t>耶鼠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>開心</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生氣</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/6jmHpF2uvVUctdn5bJCj1Q.png</t>
+  </si>
+  <si>
+    <t>嚇鼠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/4NrCEn65l1IMCjIw01f5qG.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鼠芭樂西</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1a9G2R58E6PaV5SSao5sIY.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/2clw1rviyBlnMSTf1SAoIt.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鼠搭巴酷鼠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鼠鼠咩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/2Uc4disjQp4JyULby6bewi.gif</t>
+  </si>
+  <si>
+    <t>樂不思鼠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾爾文,進擊的巨人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嚇爛</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>すばらしい,SUBARASHII,誇誇</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>社畜,誇誇</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>一ㄝㄕㄨˇ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>開心,YES</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>STARBUCKS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>開心,放假,三國</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/cQGho6pONdKb6x9bxYdoP.png</t>
+  </si>
+  <si>
+    <t>狼狼上口</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1DyI6n8tbeWHQWW3UXlNeM.png</t>
+  </si>
+  <si>
+    <t>午狼抵EMO</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EMO</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3nettowoxTLwmpgb6g4dMm.png</t>
+  </si>
+  <si>
+    <t>社畜,顧人怨</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GO狼玩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/4XbgQXkglZcQsmEEJj30X7.png</t>
+  </si>
+  <si>
+    <t>狼心狗肺</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>狼SINGLE吠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>狼</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄤˊ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>犬科</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/6kOeNcLHb8FSmihPFXYwHN.png</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3kaxijyZXLoU01iDEXT61t.png</t>
+  </si>
+  <si>
+    <t>世足</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生鮮世足</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生活</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>運動</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>足球</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄨˊㄑㄧㄡˊ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>身先士卒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3fbRf905GEAcMyCZBgfB4e.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我都林口</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪圖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>找人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄓㄠˇㄖ ㄣˊ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/4xMaIVvZaPhxiNOE9XpM69.png</t>
+  </si>
+  <si>
+    <t>快背起司</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/76DSS2sbRCa0WIRTw07jKw.png</t>
+  </si>
+  <si>
+    <t>掌芝士了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3Ki1AuK2RRFCYerPpbovmT.png</t>
+  </si>
+  <si>
+    <t>不乾式酪</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>食物</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>起司</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄑㄧˇㄙ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生氣,狗</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>知識</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3jxOoy2n9ynlLlW4X5X5j4.png</t>
+  </si>
+  <si>
+    <t>我鑰匙吊</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3tKNlX1BiKnB0I0JgcRQ8J.png</t>
+  </si>
+  <si>
+    <t>鑰匙翹翹了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/79kJaLMjUK024Qzgf5tbIn.png</t>
+  </si>
+  <si>
+    <t>冷的鑰匙</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1bOmN41fJIwCe1OGDWXCqA.png</t>
+  </si>
+  <si>
+    <t>熱的鑰匙</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>用品</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑰匙</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄠˋㄕ˙</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/4KavNWYwChDaZEWv1CV2Om.jpg</t>
+  </si>
+  <si>
+    <t>換你</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/6P4gldZNKz04QNzfpeqfb1.jpg</t>
+  </si>
+  <si>
+    <t>吃熱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1NoY8LkgvmiONQJx4uXyax.jpg</t>
+  </si>
+  <si>
+    <t>筆跟尺</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不划算</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3kPyJelL4IfmDxHdAqQWeM.jpg</t>
+  </si>
+  <si>
+    <t>美和</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>動漫</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>綜合</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>台語</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄊㄞˊㄩˇ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓦力</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>皮卡丘,寶可夢</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>賈修</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -230,6 +834,20 @@
       <family val="1"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -245,7 +863,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -268,6 +886,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -278,7 +916,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -298,6 +936,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -593,7 +1255,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z50"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
@@ -602,7 +1264,7 @@
     <col min="4" max="4" width="20.875" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="22.25" customWidth="1"/>
-    <col min="7" max="7" width="39.625" customWidth="1"/>
+    <col min="7" max="7" width="52.25" customWidth="1"/>
     <col min="8" max="8" width="22.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -676,7 +1338,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="33.75" thickBot="1">
+    <row r="3" spans="1:26" ht="17.25" thickBot="1">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
@@ -702,7 +1364,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="33.75" thickBot="1">
+    <row r="4" spans="1:26" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -728,7 +1390,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="33.75" thickBot="1">
+    <row r="5" spans="1:26" ht="17.25" thickBot="1">
       <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
@@ -754,7 +1416,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="33.75" thickBot="1">
+    <row r="6" spans="1:26" ht="17.25" thickBot="1">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -780,7 +1442,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="33.75" thickBot="1">
+    <row r="7" spans="1:26" ht="17.25" thickBot="1">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
@@ -806,7 +1468,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="33.75" thickBot="1">
+    <row r="8" spans="1:26" ht="17.25" thickBot="1">
       <c r="A8" s="3" t="s">
         <v>33</v>
       </c>
@@ -816,8 +1478,8 @@
       <c r="C8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>18</v>
+      <c r="D8" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="E8" s="4" t="b">
         <v>0</v>
@@ -842,8 +1504,8 @@
       <c r="C9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>18</v>
+      <c r="D9" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="E9" s="4" t="b">
         <v>0</v>
@@ -856,7 +1518,7 @@
       </c>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="33.75" thickBot="1">
+    <row r="10" spans="1:26" ht="17.25" thickBot="1">
       <c r="A10" s="3" t="s">
         <v>33</v>
       </c>
@@ -866,8 +1528,8 @@
       <c r="C10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>18</v>
+      <c r="D10" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="E10" s="4" t="b">
         <v>0</v>
@@ -879,10 +1541,10 @@
         <v>42</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="33.75" thickBot="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="17.25" thickBot="1">
       <c r="A11" s="3" t="s">
         <v>33</v>
       </c>
@@ -892,20 +1554,20 @@
       <c r="C11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>18</v>
+      <c r="D11" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="E11" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="17.25" thickBot="1">
@@ -918,21 +1580,21 @@
       <c r="C12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>18</v>
+      <c r="D12" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="E12" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>48</v>
-      </c>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="33.75" thickBot="1">
+    <row r="13" spans="1:26" ht="17.25" thickBot="1">
       <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
@@ -942,23 +1604,23 @@
       <c r="C13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>18</v>
+      <c r="D13" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="E13" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" ht="33.75" thickBot="1">
+    </row>
+    <row r="14" spans="1:26" ht="17.25" thickBot="1">
       <c r="A14" s="3" t="s">
         <v>33</v>
       </c>
@@ -968,41 +1630,939 @@
       <c r="C14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>18</v>
+      <c r="D14" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="E14" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H14" s="3" t="s">
+    </row>
+    <row r="15" spans="1:26" ht="17.25" thickBot="1">
+      <c r="A15" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" ht="17.25" thickBot="1">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="7" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="16" spans="1:26" ht="17.25" thickBot="1">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="A16" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A17" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A18" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A19" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A20" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A22" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A23" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A24" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A25" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A26" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H26" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A27" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="G27" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A28" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G28" t="s">
+        <v>99</v>
+      </c>
+      <c r="H28" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A29" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="H29" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A30" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H30" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A31" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H31" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A32" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G32" t="s">
+        <v>107</v>
+      </c>
+      <c r="H32" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G33" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E34" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="G34" t="s">
+        <v>119</v>
+      </c>
+      <c r="H34" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G35" t="s">
+        <v>122</v>
+      </c>
+      <c r="H35" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" t="s">
+        <v>125</v>
+      </c>
+      <c r="H36" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A37" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G37" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A38" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="G38" t="s">
+        <v>132</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A39" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A40" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="G40" t="s">
+        <v>145</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A41" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G41" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A42" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="G42" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A43" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G43" t="s">
+        <v>156</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A44" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E44" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="G44" t="s">
+        <v>158</v>
+      </c>
+      <c r="H44" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A45" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E45" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G45" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A46" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="G46" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A47" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="G47" t="s">
+        <v>167</v>
+      </c>
+      <c r="H47" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A48" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G48" t="s">
+        <v>169</v>
+      </c>
+      <c r="H48" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A49" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="G49" t="s">
+        <v>171</v>
+      </c>
+      <c r="H49" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A50" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="G50" t="s">
+        <v>174</v>
+      </c>
+      <c r="H50" t="s">
+        <v>175</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1019,9 +2579,20 @@
     <hyperlink ref="G12" r:id="rId10"/>
     <hyperlink ref="G13" r:id="rId11"/>
     <hyperlink ref="G14" r:id="rId12"/>
+    <hyperlink ref="G17" r:id="rId13"/>
+    <hyperlink ref="G18" r:id="rId14"/>
+    <hyperlink ref="G19" r:id="rId15"/>
+    <hyperlink ref="G22" r:id="rId16"/>
+    <hyperlink ref="G23" r:id="rId17"/>
+    <hyperlink ref="G25" r:id="rId18"/>
+    <hyperlink ref="G26" r:id="rId19"/>
+    <hyperlink ref="G29" r:id="rId20"/>
+    <hyperlink ref="G30" r:id="rId21"/>
+    <hyperlink ref="G31" r:id="rId22"/>
+    <hyperlink ref="G39" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
 </worksheet>
 </file>
 

--- a/scripts/memes.xlsx
+++ b/scripts/memes.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="293">
   <si>
     <t>group_keyword</t>
   </si>
@@ -791,6 +791,336 @@
   <si>
     <t>賈修</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>獵人</t>
+  </si>
+  <si>
+    <t>ㄌ一ㄝˋㄖㄣˊ</t>
+  </si>
+  <si>
+    <t>生活</t>
+  </si>
+  <si>
+    <t>職業</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3Fu03m822hza94HXCvzmP9.png</t>
+  </si>
+  <si>
+    <t>全直獵人</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/6ZWhu0JUkqryTemMrSCoGM.png</t>
+  </si>
+  <si>
+    <t>全職獵人</t>
+  </si>
+  <si>
+    <t>乘四獵人</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/4098tWM6RMLRlPm3D00JMf.png</t>
+  </si>
+  <si>
+    <t>城市獵人</t>
+  </si>
+  <si>
+    <t>美十獵人</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/7yX3ji5CowKvjQLQKnzWJB.png</t>
+  </si>
+  <si>
+    <t>美食獵人</t>
+  </si>
+  <si>
+    <t>膜霧獵人</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3GCSXutDdaMvivIsymGIdz.png</t>
+  </si>
+  <si>
+    <t>魔物獵人</t>
+  </si>
+  <si>
+    <t>飯科學</t>
+  </si>
+  <si>
+    <t>ㄈㄢˋㄎㄜㄒㄩㄝˊ</t>
+  </si>
+  <si>
+    <t>怪圖</t>
+  </si>
+  <si>
+    <t>左派右派</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/2axg9xesgGLKq9laAqewsA.png</t>
+  </si>
+  <si>
+    <t>洗米</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/5GKFQCKLx4vOYiBkRnA3zz.png</t>
+  </si>
+  <si>
+    <t>料理</t>
+  </si>
+  <si>
+    <t>路上調查</t>
+  </si>
+  <si>
+    <t>ㄌㄨˋㄕㄤˋㄉ一ㄠˋㄔㄚˊ</t>
+  </si>
+  <si>
+    <t>照片</t>
+  </si>
+  <si>
+    <t>人血器</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3CskDMbp9unZdLGh3CvXUh.jpg</t>
+  </si>
+  <si>
+    <t>蝦on蝦</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1FisQpq3peBreBjW3AXa0o.jpg</t>
+  </si>
+  <si>
+    <t>食物,海鮮</t>
+  </si>
+  <si>
+    <t>媽煮妙</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1NSVMYv44kO8oY9v5JJN4x.jpg</t>
+  </si>
+  <si>
+    <t>媽祖廟</t>
+  </si>
+  <si>
+    <t>澄香差距</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1uCc2X65VYIpFHF59PydW.jpg</t>
+  </si>
+  <si>
+    <t>城鄉差距,霹靂力矩</t>
+  </si>
+  <si>
+    <t>馬已上訴</t>
+  </si>
+  <si>
+    <t>ㄇㄚˇ一ˇㄕㄤˋㄙㄨˋ</t>
+  </si>
+  <si>
+    <t>動物</t>
+  </si>
+  <si>
+    <t>馬</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/34OiuMkZe4Ng0PN2ghHasf.jpg</t>
+  </si>
+  <si>
+    <t>主委加馬</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/4hVoKMiafPZcD7ZJZbByzH.jpg</t>
+  </si>
+  <si>
+    <t>馬卡籠</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/61G0KDgtfO3UJr3ms839Xm.jpg</t>
+  </si>
+  <si>
+    <t>馬哭都娜魯斗</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1PPyPj78EkPMoZYJriaNsz.jpg</t>
+  </si>
+  <si>
+    <t>麥當勞</t>
+  </si>
+  <si>
+    <t>泛馬泳次郎</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/5cDWIfJYPtr3lhTikuMg8A.jpg</t>
+  </si>
+  <si>
+    <t>刃牙,範馬勇次郎</t>
+  </si>
+  <si>
+    <t>榮譽馬雷人</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/2Z5mtEPHu0Qlks1SKACHbz.jpg</t>
+  </si>
+  <si>
+    <t>進擊的巨人</t>
+  </si>
+  <si>
+    <t>馬騎馬</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/35vlUgB1U7aZL3evrUuJBu.jpg</t>
+  </si>
+  <si>
+    <t>鏈鋸人,真紀真</t>
+  </si>
+  <si>
+    <t>馬來磨</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/77VV36eFUefIu6CWTfQLvC.gif</t>
+  </si>
+  <si>
+    <t>馬來貘</t>
+  </si>
+  <si>
+    <t>有點太棗</t>
+  </si>
+  <si>
+    <t>ㄧㄡˇㄉ一ㄢˇㄊㄞˋㄗㄠˇ</t>
+  </si>
+  <si>
+    <t>禮節</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/5tFcIeRKofuqtZj766MSrz.jpg</t>
+  </si>
+  <si>
+    <t>早,禮貌</t>
+  </si>
+  <si>
+    <t>有點碗了</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/CtnPDh8deC8NmappDTstM.jpg</t>
+  </si>
+  <si>
+    <t>晚,禮貌</t>
+  </si>
+  <si>
+    <t>德不腸濕</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/2jQDGxgKhpn7NfhiDZvxC3.jpg</t>
+  </si>
+  <si>
+    <t>德腸,社畜</t>
+  </si>
+  <si>
+    <t>梅裏帽</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1sIgVF12LRL57Eyxe5EcBy.jpg</t>
+  </si>
+  <si>
+    <t>禮貌</t>
+  </si>
+  <si>
+    <t>問那麼多要幹嘛</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/2WTJvZlmYeVp8irvGFtTXD.jpg</t>
+  </si>
+  <si>
+    <t>雞塊,麥當勞</t>
+  </si>
+  <si>
+    <t>這是你的venti</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/48B5EGxb0MGiscWGurXyS4.jpg</t>
+  </si>
+  <si>
+    <t>禮貌,問題</t>
+  </si>
+  <si>
+    <t>考考男</t>
+  </si>
+  <si>
+    <t>ㄎㄠˇㄎㄠˇㄋㄢˊ</t>
+  </si>
+  <si>
+    <t>鈉我烤烤你</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/6JWLz5qQvqUpsGS6LWX2fg.png</t>
+  </si>
+  <si>
+    <t>這個會考</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/24wkGxdVpFgNkYyWW79UIh.png</t>
+  </si>
+  <si>
+    <t>喜咧烤</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/5rdDGhZW0atyCvhyzfpH2V.png</t>
+  </si>
+  <si>
+    <t>BBQ,烤肉</t>
+  </si>
+  <si>
+    <t>烤烤的聲音</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/Eer3WMR5eqb05tn29PlJf.png</t>
+  </si>
+  <si>
+    <t>餅乾怪獸</t>
+  </si>
+  <si>
+    <t>本來應該</t>
+  </si>
+  <si>
+    <t>ㄅㄣˇㄌㄞˊㄧㄥㄍㄞ</t>
+  </si>
+  <si>
+    <t>蔥蔥茸茸</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/25euZQ48VFtSUu8sAhXvlZ.png</t>
+  </si>
+  <si>
+    <t>從從容容</t>
+  </si>
+  <si>
+    <t>油飪有魚</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/34UH15Eg8aBCptgTnWgZPe.png</t>
+  </si>
+  <si>
+    <t>游刃有餘</t>
+  </si>
+  <si>
+    <t>左下餃</t>
+  </si>
+  <si>
+    <t>ㄗㄨㄛˇㄒㄧㄚˋㄐㄧㄠˇ</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/6FTifUwOQgSNbtKHdxe9ap.jpg</t>
+  </si>
+  <si>
+    <t>左下角</t>
+  </si>
+  <si>
+    <t>右下餃</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1bkaFng0zvT3kyMU6PH7sy.jpg</t>
+  </si>
+  <si>
+    <t>右下角</t>
   </si>
 </sst>
 </file>
@@ -916,7 +1246,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -960,6 +1290,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1255,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z50"/>
+  <dimension ref="A1:Z86"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
@@ -2563,6 +2894,857 @@
       <c r="H50" t="s">
         <v>175</v>
       </c>
+    </row>
+    <row r="51" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A51" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A52" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E52" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A53" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E53" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A54" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A55" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A56" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H56" s="3"/>
+    </row>
+    <row r="57" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A57" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A58" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E58" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H58" s="3"/>
+    </row>
+    <row r="59" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A59" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E59" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A60" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A61" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H61" s="15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A62" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E62" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="H62" s="3"/>
+    </row>
+    <row r="63" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A63" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H63" s="3"/>
+    </row>
+    <row r="64" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A64" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E64" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H64" s="3"/>
+    </row>
+    <row r="65" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A65" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E65" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A66" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E66" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A67" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E67" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A68" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E68" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A69" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E69" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A70" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E70" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A71" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A72" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A73" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E73" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A74" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E74" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A75" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E75" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A76" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E76" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="H76" s="3"/>
+    </row>
+    <row r="77" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A77" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E77" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="H77" s="3"/>
+    </row>
+    <row r="78" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A78" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E78" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A79" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E79" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A80" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E80" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A81" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E81" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A82" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E82" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A83" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E83" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="17.25" thickBot="1">
+      <c r="D84" s="7"/>
+    </row>
+    <row r="85" spans="1:8" ht="17.25" thickBot="1">
+      <c r="D85" s="7"/>
+    </row>
+    <row r="86" spans="1:8" ht="17.25" thickBot="1">
+      <c r="D86" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -2590,9 +3772,42 @@
     <hyperlink ref="G30" r:id="rId21"/>
     <hyperlink ref="G31" r:id="rId22"/>
     <hyperlink ref="G39" r:id="rId23"/>
+    <hyperlink ref="G51" r:id="rId24"/>
+    <hyperlink ref="G52" r:id="rId25"/>
+    <hyperlink ref="G53" r:id="rId26"/>
+    <hyperlink ref="G54" r:id="rId27"/>
+    <hyperlink ref="G55" r:id="rId28"/>
+    <hyperlink ref="G56" r:id="rId29"/>
+    <hyperlink ref="G57" r:id="rId30"/>
+    <hyperlink ref="G58" r:id="rId31"/>
+    <hyperlink ref="G59" r:id="rId32"/>
+    <hyperlink ref="G60" r:id="rId33"/>
+    <hyperlink ref="G61" r:id="rId34"/>
+    <hyperlink ref="G62" r:id="rId35"/>
+    <hyperlink ref="G63" r:id="rId36"/>
+    <hyperlink ref="G64" r:id="rId37"/>
+    <hyperlink ref="G65" r:id="rId38"/>
+    <hyperlink ref="G66" r:id="rId39"/>
+    <hyperlink ref="G67" r:id="rId40"/>
+    <hyperlink ref="G68" r:id="rId41"/>
+    <hyperlink ref="G69" r:id="rId42"/>
+    <hyperlink ref="G70" r:id="rId43"/>
+    <hyperlink ref="G71" r:id="rId44"/>
+    <hyperlink ref="G72" r:id="rId45"/>
+    <hyperlink ref="G73" r:id="rId46"/>
+    <hyperlink ref="G74" r:id="rId47"/>
+    <hyperlink ref="G75" r:id="rId48"/>
+    <hyperlink ref="G76" r:id="rId49"/>
+    <hyperlink ref="G77" r:id="rId50"/>
+    <hyperlink ref="G78" r:id="rId51"/>
+    <hyperlink ref="G79" r:id="rId52"/>
+    <hyperlink ref="G80" r:id="rId53"/>
+    <hyperlink ref="G81" r:id="rId54"/>
+    <hyperlink ref="G82" r:id="rId55"/>
+    <hyperlink ref="G83" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId57"/>
 </worksheet>
 </file>
 

--- a/scripts/memes.xlsx
+++ b/scripts/memes.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="425">
   <si>
     <t>group_keyword</t>
   </si>
@@ -961,173 +961,659 @@
     <t>https://images.plurk.com/2Z5mtEPHu0Qlks1SKACHbz.jpg</t>
   </si>
   <si>
+    <t>馬騎馬</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/35vlUgB1U7aZL3evrUuJBu.jpg</t>
+  </si>
+  <si>
+    <t>鏈鋸人,真紀真</t>
+  </si>
+  <si>
+    <t>馬來磨</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/77VV36eFUefIu6CWTfQLvC.gif</t>
+  </si>
+  <si>
+    <t>馬來貘</t>
+  </si>
+  <si>
+    <t>有點太棗</t>
+  </si>
+  <si>
+    <t>ㄧㄡˇㄉ一ㄢˇㄊㄞˋㄗㄠˇ</t>
+  </si>
+  <si>
+    <t>禮節</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/5tFcIeRKofuqtZj766MSrz.jpg</t>
+  </si>
+  <si>
+    <t>早,禮貌</t>
+  </si>
+  <si>
+    <t>有點碗了</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/CtnPDh8deC8NmappDTstM.jpg</t>
+  </si>
+  <si>
+    <t>晚,禮貌</t>
+  </si>
+  <si>
+    <t>德不腸濕</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/2jQDGxgKhpn7NfhiDZvxC3.jpg</t>
+  </si>
+  <si>
+    <t>梅裏帽</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1sIgVF12LRL57Eyxe5EcBy.jpg</t>
+  </si>
+  <si>
+    <t>問那麼多要幹嘛</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/2WTJvZlmYeVp8irvGFtTXD.jpg</t>
+  </si>
+  <si>
+    <t>雞塊,麥當勞</t>
+  </si>
+  <si>
+    <t>這是你的venti</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/48B5EGxb0MGiscWGurXyS4.jpg</t>
+  </si>
+  <si>
+    <t>禮貌,問題</t>
+  </si>
+  <si>
+    <t>考考男</t>
+  </si>
+  <si>
+    <t>ㄎㄠˇㄎㄠˇㄋㄢˊ</t>
+  </si>
+  <si>
+    <t>鈉我烤烤你</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/6JWLz5qQvqUpsGS6LWX2fg.png</t>
+  </si>
+  <si>
+    <t>這個會考</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/24wkGxdVpFgNkYyWW79UIh.png</t>
+  </si>
+  <si>
+    <t>喜咧烤</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/5rdDGhZW0atyCvhyzfpH2V.png</t>
+  </si>
+  <si>
+    <t>BBQ,烤肉</t>
+  </si>
+  <si>
+    <t>烤烤的聲音</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/Eer3WMR5eqb05tn29PlJf.png</t>
+  </si>
+  <si>
+    <t>餅乾怪獸</t>
+  </si>
+  <si>
+    <t>本來應該</t>
+  </si>
+  <si>
+    <t>ㄅㄣˇㄌㄞˊㄧㄥㄍㄞ</t>
+  </si>
+  <si>
+    <t>蔥蔥茸茸</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/25euZQ48VFtSUu8sAhXvlZ.png</t>
+  </si>
+  <si>
+    <t>從從容容</t>
+  </si>
+  <si>
+    <t>油飪有魚</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/34UH15Eg8aBCptgTnWgZPe.png</t>
+  </si>
+  <si>
+    <t>游刃有餘</t>
+  </si>
+  <si>
+    <t>左下餃</t>
+  </si>
+  <si>
+    <t>ㄗㄨㄛˇㄒㄧㄚˋㄐㄧㄠˇ</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/6FTifUwOQgSNbtKHdxe9ap.jpg</t>
+  </si>
+  <si>
+    <t>左下角</t>
+  </si>
+  <si>
+    <t>右下餃</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1bkaFng0zvT3kyMU6PH7sy.jpg</t>
+  </si>
+  <si>
+    <t>右下角</t>
+  </si>
+  <si>
+    <t>莎夏</t>
+  </si>
+  <si>
+    <t>ㄕㄚㄒㄧㄚˋ</t>
+  </si>
+  <si>
+    <t>巨人</t>
+  </si>
+  <si>
+    <t>我的豆花30塊</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3x8NzoEKDnOXH0bKhRrL5P.gif</t>
+  </si>
+  <si>
+    <t>咬莎你喔</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/4Anqsrl2bVjkassntL2C03.jpg</t>
+  </si>
+  <si>
+    <t>咬殺,家庭教師</t>
+  </si>
+  <si>
+    <t>旁得蘿莎</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/4sHQDfVap2VKT8T3r8sdjn.jpg</t>
+  </si>
+  <si>
+    <t>龐德羅莎</t>
+  </si>
+  <si>
+    <t>莎瓜，我們都一樣</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3NJNmQprRUQJMJzjMdnp0w.jpg</t>
+  </si>
+  <si>
+    <t>傻瓜,歌詞</t>
+  </si>
+  <si>
+    <t>莎食車</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3k53xB8M7LVNyB96pBAZ9w.gif</t>
+  </si>
+  <si>
+    <t>砂石車,交通</t>
+  </si>
+  <si>
+    <t>莎哭啦</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/37AcMhSaJSk1WZIvAyMjW.png</t>
+  </si>
+  <si>
+    <t>さくら</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/4IX1OvWOjdF8L2nvJT52wD.jpg</t>
+  </si>
+  <si>
+    <t>莎避食</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3zfTjxIUpOpS7bR7dTWNEp.gif</t>
+  </si>
+  <si>
+    <t>SERVICE</t>
+  </si>
+  <si>
+    <t>莎騎馬</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1vAUXk7TnguYaQ21dVtJey.gif</t>
+  </si>
+  <si>
+    <t>沙其馬,食物</t>
+  </si>
+  <si>
+    <t>逗莎包</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/7uJF6tQO6XOtKpMVrZgFT4.gif</t>
+  </si>
+  <si>
+    <t>豆沙包,食物,米卡莎</t>
+  </si>
+  <si>
+    <t>ㄐㄩˋㄖㄣˊ</t>
+  </si>
+  <si>
+    <t>小里飛刀</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/7lNrt0vR2odTNW3Qd70h8d.jpg</t>
+  </si>
+  <si>
+    <t>進擊,里維,兵長</t>
+  </si>
+  <si>
+    <t>石油爾文</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/40M1pJLtyCYltVedhiXjyo.png</t>
+  </si>
+  <si>
+    <t>進擊,艾爾文,團長</t>
+  </si>
+  <si>
+    <t>皮卡丘</t>
+  </si>
+  <si>
+    <t>ㄆ一ˊㄎㄚˇㄑ一ㄡ</t>
+  </si>
+  <si>
+    <t>遊戲</t>
+  </si>
+  <si>
+    <t>一YEAH之丘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://images.plurk.com/2Vy5pyYPnKhibm41mrWyED.gif </t>
+  </si>
+  <si>
+    <t>一葉之丘,寶可夢</t>
+  </si>
+  <si>
+    <t>皮憊</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/30M6NA77tfhBrXms5N3BID.png</t>
+  </si>
+  <si>
+    <t>社畜,疲憊</t>
+  </si>
+  <si>
+    <t>多四之丘</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/2u9dVSJasaF88fCmFD6LAI.png</t>
+  </si>
+  <si>
+    <t>多事之秋,社畜</t>
+  </si>
+  <si>
+    <t>沉沒之丘</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/35iVIDPXcH8pMHkoqq6TaG.png</t>
+  </si>
+  <si>
+    <t>糧食丘</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/5mzrbVfSgqaN4jW1EiZwfK.png</t>
+  </si>
+  <si>
+    <t>梁實秋</t>
+  </si>
+  <si>
+    <t>皮卡打掐</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/5XSSKaMufj56JjReAMCltu.png</t>
+  </si>
+  <si>
+    <t>小酒窩長睫毛</t>
+  </si>
+  <si>
+    <t>ㄒㄧㄠˇㄐㄧㄡˇㄨㄛㄓㄤˇㄐㄧㄝˊㄇㄠˊ</t>
+  </si>
+  <si>
+    <t>路人超能</t>
+  </si>
+  <si>
+    <t>毛立蘭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://images.plurk.com/7xHe3JkLoYe7ivPhzaS6rc.png </t>
+  </si>
+  <si>
+    <t>毛利蘭,柯南</t>
+  </si>
+  <si>
+    <t>光是上學就很忙了</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/2XbCb6ADxPMVj2aAIDsqRM.png</t>
+  </si>
+  <si>
+    <t>棋魂,棋靈王</t>
+  </si>
+  <si>
+    <t>在傑難逃</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/2NqCnv71sVyp6l2VNes3Pn.png</t>
+  </si>
+  <si>
+    <t>在劫難逃,社畜,獵人</t>
+  </si>
+  <si>
+    <t>某靜雄</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/7scQA4gvHsVRIXsKqxH38p.gif</t>
+  </si>
+  <si>
+    <t>DRRR!,平和島靜雄,社畜,禮貌</t>
+  </si>
+  <si>
+    <t>研面浸濕</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3WF7qSXAsJs2qy6gcHRFWa.png</t>
+  </si>
+  <si>
+    <t>顏面盡失,排球少年,研磨</t>
+  </si>
+  <si>
+    <t>捶頭SON泣</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/4MbhAogHnSXF6qqmi0ezHA.png</t>
+  </si>
+  <si>
+    <t>垂頭喪氣,傷心,蠟筆小新</t>
+  </si>
+  <si>
+    <t>揍敵剋家族</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1wA4EDa4WM2UvVOMoH9GO6.jpg</t>
+  </si>
+  <si>
+    <t>獵人,揍敵剋,JOJO</t>
+  </si>
+  <si>
+    <t>廣結膳圓</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/4pNZHSZHjTaD34ebt9UbrX.png</t>
+  </si>
+  <si>
+    <t>蠟筆小新,廣志</t>
+  </si>
+  <si>
+    <t>蔡奇犽</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/6kOvGZezhlJDyGIhiPkgY0.png</t>
+  </si>
+  <si>
+    <t>菜市場,台語,獵人</t>
+  </si>
+  <si>
+    <t>ちいかわ</t>
+  </si>
+  <si>
+    <t>CHIIKAWA</t>
+  </si>
+  <si>
+    <t>攻吉</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/6IEGCnvUmFHEysXYaVgMg4.jpg</t>
+  </si>
+  <si>
+    <t>攻擊,吉伊</t>
+  </si>
+  <si>
+    <t>反吉</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/3cDgwrD2sMublrKiO7GX.jpg</t>
+  </si>
+  <si>
+    <t>反擊,吉伊</t>
+  </si>
+  <si>
+    <t>清水煮獅爺</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1a3u5lYqMNvXM2wWdIkJqO.png</t>
+  </si>
+  <si>
+    <t>清水祖師爺,獅薩</t>
+  </si>
+  <si>
+    <t>擠e卡哇</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/2qX2eAxn7Q5xunoY3RQtPj.jpg</t>
+  </si>
+  <si>
+    <t>吉伊</t>
+  </si>
+  <si>
+    <t>真嗣</t>
+  </si>
+  <si>
+    <t>ㄓㄣㄙˋ</t>
+  </si>
+  <si>
+    <t>EVA</t>
+  </si>
+  <si>
+    <t>真嗣不知道該說什麼</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1wA2dN7KnXz2MC6QlpP0QC.png</t>
+  </si>
+  <si>
+    <t>社畜,無言</t>
+  </si>
+  <si>
+    <t>真嗣服給你了</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1z4zuxdLAJeTniFhECSIdD.png</t>
+  </si>
+  <si>
+    <t>真嗣的</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/2dvGzoakJELOlzaYWQawvT.png</t>
+  </si>
+  <si>
+    <t>撒嬌</t>
+  </si>
+  <si>
+    <t>真嗣敗給你了</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/1PUKsG3FuZ8Jfe7Ec2mj7i.png</t>
+  </si>
+  <si>
+    <t>敗給你了,傻眼</t>
+  </si>
+  <si>
+    <t>真嗣羞羞臉</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/29yhgPqgY0mUKEYb3Ngd9E.png</t>
+  </si>
+  <si>
+    <t>丟臉,尷尬</t>
+  </si>
+  <si>
+    <t>真嗣想不通</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/6sVDBqSYgTyts5qNUcZCiN.png</t>
+  </si>
+  <si>
+    <t>無言,傻眼</t>
+  </si>
+  <si>
+    <t>真嗣想不開</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/6hTQ1Jo3i43e6LfjE62iPf.png</t>
+  </si>
+  <si>
+    <t>明日和奇多</t>
+  </si>
+  <si>
+    <t>ㄇㄧㄥˊㄖˋㄏㄜˊㄑㄧˊㄉㄨㄛ</t>
+  </si>
+  <si>
+    <t>零人在意</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/5ZPKbl5iOlZ9GepeJpyDZd.gif</t>
+  </si>
+  <si>
+    <t>凌波零,社畜,無言</t>
+  </si>
+  <si>
+    <t>https://images.plurk.com/6wP1RpNgfQ0GnwRJBGotq6.png</t>
+  </si>
+  <si>
+    <t>鹹食,明日香,社畜</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>加碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>請客</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬卡龍</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>進擊的巨人</t>
-  </si>
-  <si>
-    <t>馬騎馬</t>
-  </si>
-  <si>
-    <t>https://images.plurk.com/35vlUgB1U7aZL3evrUuJBu.jpg</t>
-  </si>
-  <si>
-    <t>鏈鋸人,真紀真</t>
-  </si>
-  <si>
-    <t>馬來磨</t>
-  </si>
-  <si>
-    <t>https://images.plurk.com/77VV36eFUefIu6CWTfQLvC.gif</t>
-  </si>
-  <si>
-    <t>馬來貘</t>
-  </si>
-  <si>
-    <t>有點太棗</t>
-  </si>
-  <si>
-    <t>ㄧㄡˇㄉ一ㄢˇㄊㄞˋㄗㄠˇ</t>
-  </si>
-  <si>
-    <t>禮節</t>
-  </si>
-  <si>
-    <t>https://images.plurk.com/5tFcIeRKofuqtZj766MSrz.jpg</t>
-  </si>
-  <si>
-    <t>早,禮貌</t>
-  </si>
-  <si>
-    <t>有點碗了</t>
-  </si>
-  <si>
-    <t>https://images.plurk.com/CtnPDh8deC8NmappDTstM.jpg</t>
-  </si>
-  <si>
-    <t>晚,禮貌</t>
-  </si>
-  <si>
-    <t>德不腸濕</t>
-  </si>
-  <si>
-    <t>https://images.plurk.com/2jQDGxgKhpn7NfhiDZvxC3.jpg</t>
-  </si>
-  <si>
-    <t>德腸,社畜</t>
-  </si>
-  <si>
-    <t>梅裏帽</t>
-  </si>
-  <si>
-    <t>https://images.plurk.com/1sIgVF12LRL57Eyxe5EcBy.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>進擊的巨人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>賈碧</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>禮貌</t>
-  </si>
-  <si>
-    <t>問那麼多要幹嘛</t>
-  </si>
-  <si>
-    <t>https://images.plurk.com/2WTJvZlmYeVp8irvGFtTXD.jpg</t>
-  </si>
-  <si>
-    <t>雞塊,麥當勞</t>
-  </si>
-  <si>
-    <t>這是你的venti</t>
-  </si>
-  <si>
-    <t>https://images.plurk.com/48B5EGxb0MGiscWGurXyS4.jpg</t>
-  </si>
-  <si>
-    <t>禮貌,問題</t>
-  </si>
-  <si>
-    <t>考考男</t>
-  </si>
-  <si>
-    <t>ㄎㄠˇㄎㄠˇㄋㄢˊ</t>
-  </si>
-  <si>
-    <t>鈉我烤烤你</t>
-  </si>
-  <si>
-    <t>https://images.plurk.com/6JWLz5qQvqUpsGS6LWX2fg.png</t>
-  </si>
-  <si>
-    <t>這個會考</t>
-  </si>
-  <si>
-    <t>https://images.plurk.com/24wkGxdVpFgNkYyWW79UIh.png</t>
-  </si>
-  <si>
-    <t>喜咧烤</t>
-  </si>
-  <si>
-    <t>https://images.plurk.com/5rdDGhZW0atyCvhyzfpH2V.png</t>
-  </si>
-  <si>
-    <t>BBQ,烤肉</t>
-  </si>
-  <si>
-    <t>烤烤的聲音</t>
-  </si>
-  <si>
-    <t>https://images.plurk.com/Eer3WMR5eqb05tn29PlJf.png</t>
-  </si>
-  <si>
-    <t>餅乾怪獸</t>
-  </si>
-  <si>
-    <t>本來應該</t>
-  </si>
-  <si>
-    <t>ㄅㄣˇㄌㄞˊㄧㄥㄍㄞ</t>
-  </si>
-  <si>
-    <t>蔥蔥茸茸</t>
-  </si>
-  <si>
-    <t>https://images.plurk.com/25euZQ48VFtSUu8sAhXvlZ.png</t>
-  </si>
-  <si>
-    <t>從從容容</t>
-  </si>
-  <si>
-    <t>油飪有魚</t>
-  </si>
-  <si>
-    <t>https://images.plurk.com/34UH15Eg8aBCptgTnWgZPe.png</t>
-  </si>
-  <si>
-    <t>游刃有餘</t>
-  </si>
-  <si>
-    <t>左下餃</t>
-  </si>
-  <si>
-    <t>ㄗㄨㄛˇㄒㄧㄚˋㄐㄧㄠˇ</t>
-  </si>
-  <si>
-    <t>https://images.plurk.com/6FTifUwOQgSNbtKHdxe9ap.jpg</t>
-  </si>
-  <si>
-    <t>左下角</t>
-  </si>
-  <si>
-    <t>右下餃</t>
-  </si>
-  <si>
-    <t>https://images.plurk.com/1bkaFng0zvT3kyMU6PH7sy.jpg</t>
-  </si>
-  <si>
-    <t>右下角</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>德腸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>社畜</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1177,6 +1663,12 @@
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1246,7 +1738,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1291,6 +1783,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1586,7 +2081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z86"/>
+  <dimension ref="A1:Z124"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
@@ -3197,7 +3692,9 @@
       <c r="G62" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="H62" s="3"/>
+      <c r="H62" s="3" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="63" spans="1:8" ht="17.25" thickBot="1">
       <c r="A63" s="3" t="s">
@@ -3245,7 +3742,9 @@
       <c r="G64" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="H64" s="3"/>
+      <c r="H64" s="7" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="65" spans="1:8" ht="17.25" thickBot="1">
       <c r="A65" s="3" t="s">
@@ -3322,7 +3821,7 @@
         <v>238</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>239</v>
+        <v>422</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="17.25" thickBot="1">
@@ -3342,13 +3841,13 @@
         <v>0</v>
       </c>
       <c r="F68" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G68" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="G68" s="5" t="s">
+      <c r="H68" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="17.25" thickBot="1">
@@ -3368,277 +3867,277 @@
         <v>0</v>
       </c>
       <c r="F69" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="G69" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="G69" s="5" t="s">
+      <c r="H69" s="3" t="s">
         <v>244</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="17.25" thickBot="1">
       <c r="A70" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E70" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G70" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="H70" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="17.25" thickBot="1">
       <c r="A71" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E71" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F71" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G71" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="G71" s="5" t="s">
+      <c r="H71" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="17.25" thickBot="1">
       <c r="A72" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E72" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F72" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G72" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="G72" s="5" t="s">
-        <v>255</v>
-      </c>
       <c r="H72" s="3" t="s">
-        <v>256</v>
+        <v>424</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="17.25" thickBot="1">
       <c r="A73" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E73" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="17.25" thickBot="1">
       <c r="A74" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E74" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="17.25" thickBot="1">
       <c r="A75" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E75" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="17.25" thickBot="1">
       <c r="A76" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E76" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H76" s="3"/>
     </row>
     <row r="77" spans="1:8" ht="17.25" thickBot="1">
       <c r="A77" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E77" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="H77" s="3"/>
     </row>
     <row r="78" spans="1:8" ht="17.25" thickBot="1">
       <c r="A78" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E78" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="17.25" thickBot="1">
       <c r="A79" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E79" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="17.25" thickBot="1">
       <c r="A80" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>35</v>
@@ -3650,21 +4149,21 @@
         <v>1</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="17.25" thickBot="1">
       <c r="A81" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>35</v>
@@ -3676,21 +4175,21 @@
         <v>0</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="17.25" thickBot="1">
       <c r="A82" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>35</v>
@@ -3702,21 +4201,21 @@
         <v>1</v>
       </c>
       <c r="F82" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>286</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="17.25" thickBot="1">
       <c r="A83" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>35</v>
@@ -3728,23 +4227,1074 @@
         <v>0</v>
       </c>
       <c r="F83" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A84" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="G83" s="5" t="s">
+      <c r="B84" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H83" s="3" t="s">
+      <c r="C84" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E84" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="H84" s="3"/>
+    </row>
+    <row r="85" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A85" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E85" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A86" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E86" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A87" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E87" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A88" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E88" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A89" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E89" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A90" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E90" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H90" s="3"/>
+    </row>
+    <row r="91" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A91" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E91" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A92" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E92" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A93" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E93" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="H93" s="15" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A94" s="3" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" ht="17.25" thickBot="1">
-      <c r="D84" s="7"/>
-    </row>
-    <row r="85" spans="1:8" ht="17.25" thickBot="1">
-      <c r="D85" s="7"/>
-    </row>
-    <row r="86" spans="1:8" ht="17.25" thickBot="1">
-      <c r="D86" s="7"/>
+      <c r="B94" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E94" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A95" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E95" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="H95" s="15" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A96" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E96" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A97" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E97" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A98" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E98" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A99" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E99" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A100" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E100" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A101" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E101" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="H101" s="3"/>
+    </row>
+    <row r="102" spans="1:8" ht="27" thickBot="1">
+      <c r="A102" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E102" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="27" thickBot="1">
+      <c r="A103" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E103" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="27" thickBot="1">
+      <c r="A104" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E104" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="27" thickBot="1">
+      <c r="A105" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E105" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H105" s="15" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="27" thickBot="1">
+      <c r="A106" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E106" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="H106" s="15" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="27" thickBot="1">
+      <c r="A107" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E107" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="H107" s="15" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="27" thickBot="1">
+      <c r="A108" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E108" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="H108" s="15" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="27" thickBot="1">
+      <c r="A109" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E109" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="H109" s="15" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="27" thickBot="1">
+      <c r="A110" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E110" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="27" thickBot="1">
+      <c r="A111" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E111" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="H111" s="15" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A112" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E112" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F112" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A113" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E113" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F113" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A114" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E114" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A115" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E115" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A116" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E116" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A117" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E117" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A118" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E118" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A119" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E119" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A120" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E120" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A121" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E121" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A122" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E122" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="G122" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A123" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E123" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="H123" s="15" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A124" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E124" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="H124" s="15" t="s">
+        <v>418</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -3805,9 +5355,50 @@
     <hyperlink ref="G81" r:id="rId54"/>
     <hyperlink ref="G82" r:id="rId55"/>
     <hyperlink ref="G83" r:id="rId56"/>
+    <hyperlink ref="G84" r:id="rId57"/>
+    <hyperlink ref="G85" r:id="rId58"/>
+    <hyperlink ref="G86" r:id="rId59"/>
+    <hyperlink ref="G87" r:id="rId60"/>
+    <hyperlink ref="G88" r:id="rId61"/>
+    <hyperlink ref="G89" r:id="rId62"/>
+    <hyperlink ref="G90" r:id="rId63"/>
+    <hyperlink ref="G91" r:id="rId64"/>
+    <hyperlink ref="G92" r:id="rId65"/>
+    <hyperlink ref="G93" r:id="rId66"/>
+    <hyperlink ref="G94" r:id="rId67"/>
+    <hyperlink ref="G95" r:id="rId68"/>
+    <hyperlink ref="G96" r:id="rId69" display="https://images.plurk.com/2Vy5pyYPnKhibm41mrWyED.gif"/>
+    <hyperlink ref="G97" r:id="rId70"/>
+    <hyperlink ref="G98" r:id="rId71"/>
+    <hyperlink ref="G99" r:id="rId72"/>
+    <hyperlink ref="G100" r:id="rId73"/>
+    <hyperlink ref="G101" r:id="rId74"/>
+    <hyperlink ref="G102" r:id="rId75"/>
+    <hyperlink ref="G103" r:id="rId76" display="https://images.plurk.com/7xHe3JkLoYe7ivPhzaS6rc.png"/>
+    <hyperlink ref="G104" r:id="rId77"/>
+    <hyperlink ref="G105" r:id="rId78"/>
+    <hyperlink ref="G106" r:id="rId79"/>
+    <hyperlink ref="G107" r:id="rId80"/>
+    <hyperlink ref="G108" r:id="rId81"/>
+    <hyperlink ref="G109" r:id="rId82"/>
+    <hyperlink ref="G110" r:id="rId83"/>
+    <hyperlink ref="G111" r:id="rId84"/>
+    <hyperlink ref="G112" r:id="rId85"/>
+    <hyperlink ref="G113" r:id="rId86"/>
+    <hyperlink ref="G114" r:id="rId87"/>
+    <hyperlink ref="G115" r:id="rId88"/>
+    <hyperlink ref="G116" r:id="rId89"/>
+    <hyperlink ref="G117" r:id="rId90"/>
+    <hyperlink ref="G118" r:id="rId91"/>
+    <hyperlink ref="G119" r:id="rId92"/>
+    <hyperlink ref="G120" r:id="rId93"/>
+    <hyperlink ref="G121" r:id="rId94"/>
+    <hyperlink ref="G122" r:id="rId95"/>
+    <hyperlink ref="G123" r:id="rId96"/>
+    <hyperlink ref="G124" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId57"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId98"/>
 </worksheet>
 </file>
 
